--- a/notebooks/pixel_sizes.xlsx
+++ b/notebooks/pixel_sizes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lababr\Desktop\Current Training Material - fibers only\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Labsfs\Desktop\fiber unet trainer\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2523,7 +2523,9 @@
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2">
         <v>2048</v>
@@ -2542,7 +2544,9 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2">
         <v>2048</v>
@@ -2561,7 +2565,9 @@
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2">
         <v>2048</v>
@@ -2580,7 +2586,9 @@
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2">
         <v>2048</v>
@@ -2599,7 +2607,9 @@
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2">
         <v>2048</v>
@@ -2618,7 +2628,9 @@
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2">
         <v>2048</v>
@@ -2637,7 +2649,9 @@
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2">
         <v>2048</v>
@@ -2656,7 +2670,9 @@
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2">
         <v>2048</v>
@@ -2675,7 +2691,9 @@
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2">
         <v>2048</v>
@@ -2694,7 +2712,9 @@
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2">
         <v>2048</v>
@@ -2713,7 +2733,9 @@
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
         <v>2048</v>
@@ -2732,7 +2754,9 @@
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2">
         <v>8192</v>
@@ -2751,7 +2775,9 @@
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2">
         <v>8192</v>
@@ -2770,7 +2796,9 @@
       <c r="A15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2">
         <v>8192</v>
@@ -2789,7 +2817,9 @@
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2">
         <v>8192</v>
@@ -2808,7 +2838,9 @@
       <c r="A17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2">
         <v>8192</v>
@@ -2827,7 +2859,9 @@
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
         <v>8192</v>
@@ -2846,7 +2880,9 @@
       <c r="A19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2">
         <v>2048</v>
@@ -2865,7 +2901,9 @@
       <c r="A20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2">
         <v>2048</v>
@@ -2884,7 +2922,9 @@
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="2"/>
+      <c r="B21">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2">
         <v>2048</v>
@@ -2903,7 +2943,9 @@
       <c r="A22" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2">
         <v>2048</v>
@@ -2922,7 +2964,9 @@
       <c r="A23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="2"/>
+      <c r="B23">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2">
         <v>2048</v>
@@ -2941,7 +2985,9 @@
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="2"/>
+      <c r="B24">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2">
         <v>2048</v>
@@ -2960,7 +3006,9 @@
       <c r="A25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="2"/>
+      <c r="B25">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2">
         <v>2048</v>
@@ -2979,7 +3027,9 @@
       <c r="A26" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="2"/>
+      <c r="B26">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2">
         <v>2048</v>
@@ -2998,7 +3048,9 @@
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2">
         <v>2048</v>
@@ -3017,7 +3069,9 @@
       <c r="A28" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="B28" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2">
         <v>8192</v>
@@ -3036,7 +3090,9 @@
       <c r="A29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2">
         <v>8192</v>
@@ -3055,7 +3111,9 @@
       <c r="A30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="2"/>
+      <c r="B30" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2">
         <v>8192</v>
@@ -3074,7 +3132,9 @@
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2">
         <v>8192</v>
@@ -3093,7 +3153,9 @@
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <v>8192</v>
@@ -3112,7 +3174,9 @@
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2">
         <v>8192</v>
@@ -3131,7 +3195,9 @@
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="2"/>
+      <c r="B34" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2">
         <v>8192</v>
@@ -3150,7 +3216,9 @@
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="2"/>
+      <c r="B35" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2">
         <v>8192</v>
@@ -3169,7 +3237,9 @@
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
         <v>8192</v>
@@ -3188,7 +3258,9 @@
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2">
         <v>2048</v>
@@ -3207,7 +3279,9 @@
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="2"/>
+      <c r="B38">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2">
         <v>2048</v>
@@ -3226,7 +3300,9 @@
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2">
         <v>2048</v>
@@ -3245,7 +3321,9 @@
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="2"/>
+      <c r="B40">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2">
         <v>2048</v>
@@ -3264,7 +3342,9 @@
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2">
         <v>2048</v>
@@ -3283,7 +3363,9 @@
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B42" s="2"/>
+      <c r="B42">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
         <v>2048</v>
@@ -3302,7 +3384,9 @@
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B43" s="2"/>
+      <c r="B43">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2">
         <v>2048</v>
@@ -3321,7 +3405,9 @@
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="2"/>
+      <c r="B44">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2">
         <v>2048</v>
@@ -3340,7 +3426,9 @@
       <c r="A45" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B45" s="2"/>
+      <c r="B45">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2">
         <v>2048</v>
@@ -3359,7 +3447,9 @@
       <c r="A46" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="2"/>
+      <c r="B46">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2">
         <v>2048</v>
@@ -3378,7 +3468,9 @@
       <c r="A47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B47" s="2"/>
+      <c r="B47">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
         <v>2048</v>
@@ -3397,7 +3489,9 @@
       <c r="A48" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B48" s="2"/>
+      <c r="B48">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
         <v>2048</v>
@@ -3416,7 +3510,9 @@
       <c r="A49" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B49" s="2"/>
+      <c r="B49">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
         <v>2048</v>
@@ -3435,7 +3531,9 @@
       <c r="A50" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B50" s="2"/>
+      <c r="B50">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2">
         <v>2048</v>
@@ -3454,7 +3552,9 @@
       <c r="A51" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="2"/>
+      <c r="B51">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
         <v>2048</v>
@@ -3473,7 +3573,9 @@
       <c r="A52" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="2"/>
+      <c r="B52">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
         <v>2048</v>
@@ -3492,7 +3594,9 @@
       <c r="A53" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
         <v>8192</v>
@@ -3511,7 +3615,9 @@
       <c r="A54" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B54" s="2"/>
+      <c r="B54" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
         <v>8192</v>
@@ -3530,7 +3636,9 @@
       <c r="A55" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B55" s="2"/>
+      <c r="B55">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2">
         <v>2048</v>
@@ -3549,7 +3657,9 @@
       <c r="A56" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B56" s="2"/>
+      <c r="B56">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
         <v>2048</v>
@@ -3568,7 +3678,9 @@
       <c r="A57" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B57" s="2"/>
+      <c r="B57">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
         <v>2048</v>
@@ -3587,7 +3699,9 @@
       <c r="A58" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B58" s="2"/>
+      <c r="B58">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
         <v>2048</v>
@@ -3606,7 +3720,9 @@
       <c r="A59" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B59" s="2"/>
+      <c r="B59">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
         <v>2048</v>
@@ -3625,7 +3741,9 @@
       <c r="A60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B60" s="2"/>
+      <c r="B60">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
         <v>2048</v>
@@ -3644,7 +3762,9 @@
       <c r="A61" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="2"/>
+      <c r="B61">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
         <v>2048</v>
@@ -3663,7 +3783,9 @@
       <c r="A62" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B62" s="2"/>
+      <c r="B62">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
         <v>2048</v>
@@ -3682,7 +3804,9 @@
       <c r="A63" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="2"/>
+      <c r="B63">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
         <v>2048</v>
@@ -3701,7 +3825,9 @@
       <c r="A64" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B64" s="2"/>
+      <c r="B64">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2">
         <v>2048</v>
@@ -3720,7 +3846,9 @@
       <c r="A65" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B65" s="2"/>
+      <c r="B65">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2">
         <v>2048</v>
@@ -3739,7 +3867,9 @@
       <c r="A66" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="2"/>
+      <c r="B66">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2">
         <v>2048</v>
@@ -3758,7 +3888,9 @@
       <c r="A67" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B67" s="2"/>
+      <c r="B67">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
         <v>2048</v>
@@ -3777,7 +3909,9 @@
       <c r="A68" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B68" s="2"/>
+      <c r="B68">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
         <v>2048</v>
@@ -3796,7 +3930,9 @@
       <c r="A69" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B69" s="2"/>
+      <c r="B69" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
         <v>8192</v>
@@ -3815,7 +3951,9 @@
       <c r="A70" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B70" s="2"/>
+      <c r="B70" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2">
         <v>8192</v>
@@ -3834,7 +3972,9 @@
       <c r="A71" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B71" s="2"/>
+      <c r="B71">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
         <v>2048</v>
@@ -3853,7 +3993,9 @@
       <c r="A72" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B72" s="2"/>
+      <c r="B72">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
         <v>2048</v>
@@ -3872,7 +4014,9 @@
       <c r="A73" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B73" s="2"/>
+      <c r="B73">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2">
         <v>2048</v>
@@ -3891,7 +4035,9 @@
       <c r="A74" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2">
         <v>2048</v>
@@ -3910,7 +4056,9 @@
       <c r="A75" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B75" s="2"/>
+      <c r="B75">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2">
         <v>2048</v>
@@ -3929,7 +4077,9 @@
       <c r="A76" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2">
         <v>8192</v>
@@ -3948,7 +4098,9 @@
       <c r="A77" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2">
         <v>8192</v>
@@ -3967,7 +4119,9 @@
       <c r="A78" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2">
         <v>8192</v>
@@ -3986,7 +4140,9 @@
       <c r="A79" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2">
         <v>8192</v>
@@ -4005,7 +4161,9 @@
       <c r="A80" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2">
         <v>8192</v>
@@ -4024,7 +4182,9 @@
       <c r="A81" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2">
         <v>8192</v>
@@ -4043,7 +4203,9 @@
       <c r="A82" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2">
         <v>2048</v>
@@ -4062,7 +4224,9 @@
       <c r="A83" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2">
         <v>2048</v>
@@ -4081,7 +4245,9 @@
       <c r="A84" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2">
+        <v>50.885420970388402</v>
+      </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2">
         <v>8192</v>
@@ -4100,7 +4266,9 @@
       <c r="A85" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2">
         <v>2048</v>
@@ -4119,7 +4287,9 @@
       <c r="A86" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2">
         <v>2048</v>
@@ -4138,7 +4308,9 @@
       <c r="A87" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2">
         <v>2048</v>
@@ -4157,7 +4329,9 @@
       <c r="A88" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2">
         <v>2048</v>
@@ -4176,7 +4350,9 @@
       <c r="A89" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2">
         <v>2048</v>
@@ -4195,7 +4371,9 @@
       <c r="A90" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90">
+        <v>25.449209261818801</v>
+      </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2">
         <v>2048</v>
